--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Quilaco</t>
   </si>
   <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Alamos</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:22</t>
+    <t xml:space="preserve">2026-09-09 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -999,7 +999,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8106</v>
+        <v>8311</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
@@ -1016,7 +1016,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8311</v>
+        <v>8106</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:18</t>
+    <t xml:space="preserve">2026-09-17 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Quilaco</t>
   </si>
   <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Alamos</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:13</t>
+    <t xml:space="preserve">2026-09-23 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -999,7 +999,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8311</v>
+        <v>8106</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
@@ -1016,7 +1016,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8106</v>
+        <v>8311</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:42</t>
+    <t xml:space="preserve">2026-10-02 14:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Cañete</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:58</t>
+    <t xml:space="preserve">2026-10-04 09:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:12</t>
+    <t xml:space="preserve">2026-10-05 11:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
